--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -127,19 +127,19 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20137260</t>
-  </si>
-  <si>
-    <t>B/D FW ACNE CARE 100</t>
-  </si>
-  <si>
-    <t>20042866</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT150</t>
+    <t>20073377</t>
+  </si>
+  <si>
+    <t>GRNIER MC.CLN PNK125</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20132715</t>
+  </si>
+  <si>
+    <t>GLAD2 MOIST BLBRRY30</t>
   </si>
   <si>
     <t>20067210</t>
@@ -960,15 +960,15 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1240,7 +1240,7 @@
         <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070380</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN PCS</t>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
     <t>EG0A</t>
@@ -28,259 +28,154 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2H)</t>
-  </si>
-  <si>
-    <t>20046368</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN 250</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20024699</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 62G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20016388</t>
-  </si>
-  <si>
-    <t>KRM TUNISIA HIJRA500</t>
+    <t>20039717</t>
+  </si>
+  <si>
+    <t>CADBURY DAIRY MLK 52</t>
+  </si>
+  <si>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
+  </si>
+  <si>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20113402</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH E&amp;B 100</t>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>20135430</t>
+  </si>
+  <si>
+    <t>LAURIER RN 18'S 35CM</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20131300</t>
+  </si>
+  <si>
+    <t>LAURIER NAT.C 16S-30</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20120202</t>
+  </si>
+  <si>
+    <t>LAURIER P/LINER NC40</t>
+  </si>
+  <si>
+    <t>20019342</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GUARD 10</t>
+  </si>
+  <si>
+    <t>20106051</t>
+  </si>
+  <si>
+    <t>SOFTEX DS WG 30'S/23</t>
+  </si>
+  <si>
+    <t>20133708</t>
+  </si>
+  <si>
+    <t>SFTEX PW CMF/NGHT18S</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20073377</t>
-  </si>
-  <si>
-    <t>GRNIER MC.CLN PNK125</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20132715</t>
-  </si>
-  <si>
-    <t>GLAD2 MOIST BLBRRY30</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138098</t>
-  </si>
-  <si>
-    <t>SCORA GENTLE CLEAN75</t>
-  </si>
-  <si>
-    <t>20137173</t>
-  </si>
-  <si>
-    <t>SCRLETT EDP VEL.R 30</t>
-  </si>
-  <si>
-    <t>20137253</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP COOL 100M</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20053183</t>
-  </si>
-  <si>
-    <t>GTSBY STYL POMADE 75</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t>IDM COSMETIC HADIAH</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>10032895</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT GW 11/35</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>20132821</t>
-  </si>
-  <si>
-    <t>YNKN WIPE HND&amp;MTH2'S</t>
-  </si>
-  <si>
-    <t>20082445</t>
-  </si>
-  <si>
-    <t>MP BB WIPES N/FR BDD</t>
-  </si>
-  <si>
-    <t>10026930</t>
-  </si>
-  <si>
-    <t>JHNSN H&amp;B MLK+RC 200</t>
-  </si>
-  <si>
-    <t>20008706</t>
-  </si>
-  <si>
-    <t>MASTER CLG SPRMN 100</t>
-  </si>
-  <si>
-    <t>20130478</t>
-  </si>
-  <si>
-    <t>DOREMI COLG GLACR100</t>
-  </si>
-  <si>
-    <t>10031470</t>
-  </si>
-  <si>
-    <t>MY BABY PWD S.FLO225</t>
-  </si>
-  <si>
-    <t>10011772</t>
-  </si>
-  <si>
-    <t>CUSSONS B/CRM MILD50</t>
-  </si>
-  <si>
-    <t>10033930</t>
-  </si>
-  <si>
-    <t>CUSSON B/CRM SOFT50</t>
-  </si>
-  <si>
-    <t>20020120</t>
-  </si>
-  <si>
-    <t>CUSSON H&amp;BW ML&amp;G 375</t>
-  </si>
-  <si>
-    <t>20135778</t>
-  </si>
-  <si>
-    <t>CSSONS H&amp;B DP.MST375</t>
-  </si>
-  <si>
-    <t>20135637</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B WSH 300</t>
-  </si>
-  <si>
-    <t>20115501</t>
-  </si>
-  <si>
-    <t>KODOMO P/G MIXBRY45</t>
-  </si>
-  <si>
-    <t>20062263</t>
-  </si>
-  <si>
-    <t>PIGEON PRS NPL L 3'S</t>
-  </si>
-  <si>
-    <t>RT</t>
+    <t>20141367</t>
+  </si>
+  <si>
+    <t>HERS CL BRZE 12'S-30</t>
   </si>
 </sst>
 </file>
@@ -673,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -717,18 +612,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -737,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -754,13 +649,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -774,613 +669,333 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,23 +11,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="65">
   <si>
     <t/>
   </si>
   <si>
+    <t>20070380</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN PCS</t>
+  </si>
+  <si>
+    <t>EG0A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-2H)</t>
+  </si>
+  <si>
+    <t>20046368</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN 250</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20016388</t>
+  </si>
+  <si>
+    <t>KRM TUNISIA HIJRA500</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20015737</t>
   </si>
   <si>
     <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
-    <t>EG0A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -49,24 +79,27 @@
     <t>STT FRENCH FRIES 62G</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20039717</t>
   </si>
   <si>
     <t>CADBURY DAIRY MLK 52</t>
   </si>
   <si>
+    <t>20140456</t>
+  </si>
+  <si>
+    <t>WONG COCO PEDAS 220G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
     <t>20140229</t>
   </si>
   <si>
     <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
     <t>20125696</t>
   </si>
   <si>
@@ -86,9 +119,6 @@
   </si>
   <si>
     <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>20087542</t>
@@ -568,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -612,18 +642,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -632,10 +662,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -649,13 +679,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -669,133 +699,133 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -809,53 +839,53 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,7 +899,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
@@ -889,13 +919,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,13 +939,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,53 +959,53 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,13 +1019,93 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
   <si>
     <t/>
   </si>
@@ -73,16 +73,43 @@
     <t>5</t>
   </si>
   <si>
-    <t>20024699</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 62G</t>
-  </si>
-  <si>
-    <t>20039717</t>
-  </si>
-  <si>
-    <t>CADBURY DAIRY MLK 52</t>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20139813</t>
+  </si>
+  <si>
+    <t>BIOKUL MRSHMALLOW 80</t>
+  </si>
+  <si>
+    <t>20139859</t>
+  </si>
+  <si>
+    <t>BIOKUL BROWN SGR 80</t>
+  </si>
+  <si>
+    <t>20139814</t>
+  </si>
+  <si>
+    <t>BIOKUL TO GO YUZU 80</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>20140456</t>
@@ -91,121 +118,154 @@
     <t>WONG COCO PEDAS 220G</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
     <t>20139289</t>
   </si>
   <si>
     <t>LARISST VANILLA 360G</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>20135430</t>
-  </si>
-  <si>
-    <t>LAURIER RN 18'S 35CM</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>20141134</t>
+  </si>
+  <si>
+    <t>POCKY STRAW YOGRT 38</t>
+  </si>
+  <si>
+    <t>20058061</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT CHR/B 100</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20075951</t>
+  </si>
+  <si>
+    <t>MKRZO HES MR.DEW 100</t>
+  </si>
+  <si>
+    <t>20078998</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT WHT MS100</t>
+  </si>
+  <si>
+    <t>20129466</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT AMB WD100</t>
+  </si>
+  <si>
+    <t>20013924</t>
+  </si>
+  <si>
+    <t>MIRANDA HC NAT.BLACK</t>
+  </si>
+  <si>
+    <t>20013925</t>
+  </si>
+  <si>
+    <t>MRNDA BLCG/DCLR MC-6</t>
+  </si>
+  <si>
+    <t>20140969</t>
+  </si>
+  <si>
+    <t>PANTENE INT.SHOT 4'S</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20082205</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP HFT 170</t>
+  </si>
+  <si>
+    <t>20082206</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP DT 170</t>
+  </si>
+  <si>
+    <t>20139602</t>
+  </si>
+  <si>
+    <t>AZZURA DB FC WSH 100</t>
+  </si>
+  <si>
+    <t>20138898</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 160</t>
+  </si>
+  <si>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
+  </si>
+  <si>
+    <t>20091441</t>
+  </si>
+  <si>
+    <t>CLEAR SHP KOMPLIT160</t>
+  </si>
+  <si>
+    <t>20091440</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL160</t>
+  </si>
+  <si>
+    <t>20136021</t>
+  </si>
+  <si>
+    <t>GTSBY FBR PMD GLOS80</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20131300</t>
-  </si>
-  <si>
-    <t>LAURIER NAT.C 16S-30</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20120202</t>
-  </si>
-  <si>
-    <t>LAURIER P/LINER NC40</t>
-  </si>
-  <si>
-    <t>20019342</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GUARD 10</t>
-  </si>
-  <si>
-    <t>20106051</t>
-  </si>
-  <si>
-    <t>SOFTEX DS WG 30'S/23</t>
-  </si>
-  <si>
-    <t>20133708</t>
-  </si>
-  <si>
-    <t>SFTEX PW CMF/NGHT18S</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10032895</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT GW 11/35</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20141367</t>
-  </si>
-  <si>
-    <t>HERS CL BRZE 12'S-30</t>
+    <t>20140223</t>
+  </si>
+  <si>
+    <t>LOREAL SHP F.R3X 200</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
 </sst>
 </file>
@@ -598,13 +658,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -785,15 +846,15 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -805,15 +866,15 @@
         <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -825,15 +886,15 @@
         <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -842,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -850,39 +911,39 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>16</v>
@@ -890,10 +951,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -902,18 +963,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -922,7 +983,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
@@ -930,10 +991,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -942,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>16</v>
@@ -950,22 +1011,22 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -982,7 +1043,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>50</v>
@@ -1002,7 +1063,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>50</v>
@@ -1022,7 +1083,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>50</v>
@@ -1039,10 +1100,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>50</v>
@@ -1059,53 +1120,233 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>59</v>
+      <c r="F29" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="100">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070380</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN PCS</t>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
     <t>EG0A</t>
@@ -28,241 +28,286 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2H)</t>
-  </si>
-  <si>
-    <t>20046368</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN 250</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20016388</t>
-  </si>
-  <si>
-    <t>KRM TUNISIA HIJRA500</t>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
+    <t>10004061</t>
+  </si>
+  <si>
+    <t>W/COCO ICE BON2 5'S</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20139813</t>
-  </si>
-  <si>
-    <t>BIOKUL MRSHMALLOW 80</t>
-  </si>
-  <si>
-    <t>20139859</t>
-  </si>
-  <si>
-    <t>BIOKUL BROWN SGR 80</t>
-  </si>
-  <si>
-    <t>20139814</t>
-  </si>
-  <si>
-    <t>BIOKUL TO GO YUZU 80</t>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>10020995</t>
+  </si>
+  <si>
+    <t>W/COCO LYCHEE 1KG</t>
+  </si>
+  <si>
+    <t>10021003</t>
+  </si>
+  <si>
+    <t>W/COCO CCPD SLC 1KG</t>
+  </si>
+  <si>
+    <t>10020713</t>
+  </si>
+  <si>
+    <t>WG COCO CUBE CP 1KG</t>
+  </si>
+  <si>
     <t>20140456</t>
   </si>
   <si>
     <t>WONG COCO PEDAS 220G</t>
   </si>
   <si>
+    <t>20137599</t>
+  </si>
+  <si>
+    <t>IDMLK YGRT BN.BRS 70</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20137602</t>
+  </si>
+  <si>
+    <t>IDMLK YGRT BLUBRY 70</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>20069701</t>
+  </si>
+  <si>
+    <t>MEG KEJU SRBGN 160G</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20136649</t>
+  </si>
+  <si>
+    <t>DIAMOND JC CRANBR200</t>
+  </si>
+  <si>
+    <t>20137601</t>
+  </si>
+  <si>
+    <t>IDMLK YOGRT STRAW 70</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
+    <t>10006955</t>
+  </si>
+  <si>
+    <t>SELECTION KAPAS 50GR</t>
+  </si>
+  <si>
+    <t>20083934</t>
+  </si>
+  <si>
+    <t>KOJIESAN SL SOAP 65</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20073377</t>
+  </si>
+  <si>
+    <t>GRNIER MC.CLN PNK125</t>
+  </si>
+  <si>
+    <t>20138098</t>
+  </si>
+  <si>
+    <t>SCORA GENTLE CLEAN75</t>
+  </si>
+  <si>
+    <t>10015461</t>
+  </si>
+  <si>
+    <t>OVALE FACIAL WHIT200</t>
+  </si>
+  <si>
+    <t>10028739</t>
+  </si>
+  <si>
+    <t>VIVA MILK CLN BGK100</t>
+  </si>
+  <si>
+    <t>RT,(E-7B)</t>
+  </si>
+  <si>
+    <t>20137011</t>
+  </si>
+  <si>
+    <t>THE/O HYL MC.WTR 300</t>
+  </si>
+  <si>
+    <t>20092317</t>
+  </si>
+  <si>
+    <t>POISE FAC.FM WHT 100</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20134060</t>
+  </si>
+  <si>
+    <t>GLAD2 CLNSR BLBRRY70</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20137260</t>
+  </si>
+  <si>
+    <t>B/D FW ACNE CARE 100</t>
+  </si>
+  <si>
+    <t>20125542</t>
+  </si>
+  <si>
+    <t>KAHF OIL&amp;CMED DEF100</t>
+  </si>
+  <si>
+    <t>20046907</t>
+  </si>
+  <si>
+    <t>BIORE MEN COOL/O 100</t>
+  </si>
+  <si>
+    <t>20018965</t>
+  </si>
+  <si>
+    <t>NIVEA FF DRK.SPT 100</t>
+  </si>
+  <si>
+    <t>20046688</t>
+  </si>
+  <si>
+    <t>PONDS PW WHT.BS 100</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20052043</t>
+  </si>
+  <si>
+    <t>GRNIER MEN WSABI 100</t>
+  </si>
+  <si>
+    <t>20134797</t>
+  </si>
+  <si>
+    <t>WRDH UV ACN/CL SUN35</t>
+  </si>
+  <si>
+    <t>20079010</t>
+  </si>
+  <si>
+    <t>SHNZUI F.WASH TUB 80</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>20141134</t>
-  </si>
-  <si>
-    <t>POCKY STRAW YOGRT 38</t>
-  </si>
-  <si>
-    <t>20058061</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT CHR/B 100</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20075951</t>
-  </si>
-  <si>
-    <t>MKRZO HES MR.DEW 100</t>
-  </si>
-  <si>
-    <t>20078998</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT WHT MS100</t>
-  </si>
-  <si>
-    <t>20129466</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT AMB WD100</t>
-  </si>
-  <si>
-    <t>20013924</t>
-  </si>
-  <si>
-    <t>MIRANDA HC NAT.BLACK</t>
-  </si>
-  <si>
-    <t>20013925</t>
-  </si>
-  <si>
-    <t>MRNDA BLCG/DCLR MC-6</t>
-  </si>
-  <si>
-    <t>20140969</t>
-  </si>
-  <si>
-    <t>PANTENE INT.SHOT 4'S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20082205</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP HFT 170</t>
-  </si>
-  <si>
-    <t>20082206</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP DT 170</t>
-  </si>
-  <si>
-    <t>20139602</t>
-  </si>
-  <si>
-    <t>AZZURA DB FC WSH 100</t>
-  </si>
-  <si>
-    <t>20138898</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 160</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>20091441</t>
-  </si>
-  <si>
-    <t>CLEAR SHP KOMPLIT160</t>
-  </si>
-  <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
-  </si>
-  <si>
-    <t>20136021</t>
-  </si>
-  <si>
-    <t>GTSBY FBR PMD GLOS80</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20140223</t>
-  </si>
-  <si>
-    <t>LOREAL SHP F.R3X 200</t>
+    <t>20040194</t>
+  </si>
+  <si>
+    <t>GRNR BC FWS.VT.C100</t>
+  </si>
+  <si>
+    <t>20052782</t>
+  </si>
+  <si>
+    <t>GRNIER SKR GLW HY100</t>
+  </si>
+  <si>
+    <t>20021810</t>
+  </si>
+  <si>
+    <t>ACNES CREAMY WASH100</t>
   </si>
   <si>
     <t>11</t>
@@ -658,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -726,15 +771,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -743,18 +788,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -763,18 +808,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -783,30 +828,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -823,10 +868,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,10 +888,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -863,10 +908,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -883,10 +928,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -903,10 +948,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -923,190 +968,190 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1120,13 +1165,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1140,13 +1185,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1160,33 +1205,33 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1200,13 +1245,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1220,113 +1265,113 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1340,13 +1385,133 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>50</v>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="59">
   <si>
     <t/>
   </si>
   <si>
-    <t>20015737</t>
-  </si>
-  <si>
-    <t>IDM NATA DE COCO 900</t>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
   </si>
   <si>
     <t>EG0A</t>
@@ -28,18 +28,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20139289</t>
   </si>
   <si>
@@ -103,214 +97,97 @@
     <t>WONG COCO PEDAS 220G</t>
   </si>
   <si>
-    <t>20137599</t>
-  </si>
-  <si>
-    <t>IDMLK YGRT BN.BRS 70</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20137602</t>
-  </si>
-  <si>
-    <t>IDMLK YGRT BLUBRY 70</t>
-  </si>
-  <si>
-    <t>20126424</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 115G</t>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>20021029</t>
+  </si>
+  <si>
+    <t>QTELA KRPK BLDO 175G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20134456</t>
+  </si>
+  <si>
+    <t>JAPOTA SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20069696</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN KRML100</t>
+  </si>
+  <si>
+    <t>20042370</t>
+  </si>
+  <si>
+    <t>M/SUKA R/LAUT PNG 9G</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>20069701</t>
-  </si>
-  <si>
-    <t>MEG KEJU SRBGN 160G</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20136649</t>
-  </si>
-  <si>
-    <t>DIAMOND JC CRANBR200</t>
-  </si>
-  <si>
-    <t>20137601</t>
-  </si>
-  <si>
-    <t>IDMLK YOGRT STRAW 70</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10006955</t>
-  </si>
-  <si>
-    <t>SELECTION KAPAS 50GR</t>
-  </si>
-  <si>
-    <t>20083934</t>
-  </si>
-  <si>
-    <t>KOJIESAN SL SOAP 65</t>
+    <t>20057442</t>
+  </si>
+  <si>
+    <t>KINDER/J CHOC BOYS20</t>
+  </si>
+  <si>
+    <t>20057444</t>
+  </si>
+  <si>
+    <t>KINDER/J CHOC GIRL20</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOC 100G</t>
+  </si>
+  <si>
+    <t>10008550</t>
+  </si>
+  <si>
+    <t>G/T CHOCHP DB.CHO 72</t>
+  </si>
+  <si>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>10000103</t>
+  </si>
+  <si>
+    <t>REGAL MARIE 230GR</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20073377</t>
-  </si>
-  <si>
-    <t>GRNIER MC.CLN PNK125</t>
-  </si>
-  <si>
-    <t>20138098</t>
-  </si>
-  <si>
-    <t>SCORA GENTLE CLEAN75</t>
-  </si>
-  <si>
-    <t>10015461</t>
-  </si>
-  <si>
-    <t>OVALE FACIAL WHIT200</t>
-  </si>
-  <si>
-    <t>10028739</t>
-  </si>
-  <si>
-    <t>VIVA MILK CLN BGK100</t>
-  </si>
-  <si>
-    <t>RT,(E-7B)</t>
-  </si>
-  <si>
-    <t>20137011</t>
-  </si>
-  <si>
-    <t>THE/O HYL MC.WTR 300</t>
-  </si>
-  <si>
-    <t>20092317</t>
-  </si>
-  <si>
-    <t>POISE FAC.FM WHT 100</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20134060</t>
-  </si>
-  <si>
-    <t>GLAD2 CLNSR BLBRRY70</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20137260</t>
-  </si>
-  <si>
-    <t>B/D FW ACNE CARE 100</t>
-  </si>
-  <si>
-    <t>20125542</t>
-  </si>
-  <si>
-    <t>KAHF OIL&amp;CMED DEF100</t>
-  </si>
-  <si>
-    <t>20046907</t>
-  </si>
-  <si>
-    <t>BIORE MEN COOL/O 100</t>
-  </si>
-  <si>
-    <t>20018965</t>
-  </si>
-  <si>
-    <t>NIVEA FF DRK.SPT 100</t>
-  </si>
-  <si>
-    <t>20046688</t>
-  </si>
-  <si>
-    <t>PONDS PW WHT.BS 100</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20052043</t>
-  </si>
-  <si>
-    <t>GRNIER MEN WSABI 100</t>
-  </si>
-  <si>
-    <t>20134797</t>
-  </si>
-  <si>
-    <t>WRDH UV ACN/CL SUN35</t>
-  </si>
-  <si>
-    <t>20079010</t>
-  </si>
-  <si>
-    <t>SHNZUI F.WASH TUB 80</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20040194</t>
-  </si>
-  <si>
-    <t>GRNR BC FWS.VT.C100</t>
-  </si>
-  <si>
-    <t>20052782</t>
-  </si>
-  <si>
-    <t>GRNIER SKR GLW HY100</t>
-  </si>
-  <si>
-    <t>20021810</t>
-  </si>
-  <si>
-    <t>ACNES CREAMY WASH100</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
 </sst>
 </file>
@@ -703,14 +580,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -748,18 +624,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -768,18 +644,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -788,18 +664,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -808,18 +684,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -828,30 +704,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -865,13 +741,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -885,13 +761,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -905,13 +781,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -925,13 +801,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -945,33 +821,33 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,533 +861,213 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,183 +11,240 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
   <si>
     <t/>
   </si>
   <si>
+    <t>10004061</t>
+  </si>
+  <si>
+    <t>W/COCO ICE BON2 5'S</t>
+  </si>
+  <si>
+    <t>EG0A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
     <t>20139288</t>
   </si>
   <si>
     <t>LARISST COCOPANDN360</t>
   </si>
   <si>
-    <t>EG0A</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20140456</t>
+  </si>
+  <si>
+    <t>WONG COCO PEDAS 220G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20140229</t>
   </si>
   <si>
     <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>10020995</t>
-  </si>
-  <si>
-    <t>W/COCO LYCHEE 1KG</t>
-  </si>
-  <si>
-    <t>10021003</t>
-  </si>
-  <si>
-    <t>W/COCO CCPD SLC 1KG</t>
-  </si>
-  <si>
-    <t>10020713</t>
-  </si>
-  <si>
-    <t>WG COCO CUBE CP 1KG</t>
-  </si>
-  <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>20021029</t>
-  </si>
-  <si>
-    <t>QTELA KRPK BLDO 175G</t>
+    <t>20088712</t>
+  </si>
+  <si>
+    <t>SASA SANT.KLP CAIR65</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
+  </si>
+  <si>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
   </si>
   <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20134456</t>
-  </si>
-  <si>
-    <t>JAPOTA SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20069696</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN KRML100</t>
-  </si>
-  <si>
-    <t>20042370</t>
-  </si>
-  <si>
-    <t>M/SUKA R/LAUT PNG 9G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20057442</t>
-  </si>
-  <si>
-    <t>KINDER/J CHOC BOYS20</t>
-  </si>
-  <si>
-    <t>20057444</t>
-  </si>
-  <si>
-    <t>KINDER/J CHOC GIRL20</t>
-  </si>
-  <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>10008550</t>
-  </si>
-  <si>
-    <t>G/T CHOCHP DB.CHO 72</t>
-  </si>
-  <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>10000103</t>
-  </si>
-  <si>
-    <t>REGAL MARIE 230GR</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>20116410</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 75G</t>
+  </si>
+  <si>
+    <t>20039717</t>
+  </si>
+  <si>
+    <t>CADBURY DAIRY MLK 52</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
+  </si>
+  <si>
+    <t>20141978</t>
+  </si>
+  <si>
+    <t>GARNIER VITC LWPH100</t>
+  </si>
+  <si>
+    <t>20141979</t>
+  </si>
+  <si>
+    <t>GARNIER SKR GLOW 100</t>
+  </si>
+  <si>
+    <t>20142123</t>
+  </si>
+  <si>
+    <t>BDL FW PAPAYA 100G</t>
+  </si>
+  <si>
+    <t>20110001</t>
+  </si>
+  <si>
+    <t>WARDAH UV GRD GEL40</t>
+  </si>
+  <si>
+    <t>20127466</t>
+  </si>
+  <si>
+    <t>IMPLRA SPF40 SS 50ML</t>
+  </si>
+  <si>
+    <t>10028739</t>
+  </si>
+  <si>
+    <t>VIVA MILK CLN BGK100</t>
+  </si>
+  <si>
+    <t>RT,(E-7B)</t>
+  </si>
+  <si>
+    <t>20135594</t>
+  </si>
+  <si>
+    <t>CARASUN SS UV.SUNS30</t>
+  </si>
+  <si>
+    <t>20138590</t>
+  </si>
+  <si>
+    <t>HNSUI BRGH/E MOIS 30</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20133672</t>
+  </si>
+  <si>
+    <t>HNSUI COL.SUNS.SPF50</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20138592</t>
+  </si>
+  <si>
+    <t>HNSUI MICELAR WTR300</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -580,13 +637,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -624,18 +682,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -644,10 +702,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -667,15 +725,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -684,130 +742,130 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,101 +879,101 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -927,15 +985,15 @@
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -944,18 +1002,18 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -964,18 +1022,18 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -987,15 +1045,15 @@
         <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1004,70 +1062,210 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
   <si>
     <t/>
   </si>
@@ -76,175 +76,181 @@
     <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20088712</t>
-  </si>
-  <si>
-    <t>SASA SANT.KLP CAIR65</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>20022908</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY ALMOND 82</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20084444</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A.KCP129</t>
+  </si>
+  <si>
+    <t>20129436</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 RDANG132</t>
+  </si>
+  <si>
+    <t>20138877</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 ACEH 140</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
+  </si>
+  <si>
+    <t>20063027</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT.PDS 270</t>
+  </si>
+  <si>
+    <t>20064412</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL ASLI 270</t>
+  </si>
+  <si>
+    <t>10036570</t>
+  </si>
+  <si>
+    <t>ABC SARDINES CHLI155</t>
+  </si>
+  <si>
+    <t>10036569</t>
+  </si>
+  <si>
+    <t>ABC SRDINES TOMT 155</t>
+  </si>
+  <si>
+    <t>10027529</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 265</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
-  </si>
-  <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20116410</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 75G</t>
-  </si>
-  <si>
-    <t>20039717</t>
-  </si>
-  <si>
-    <t>CADBURY DAIRY MLK 52</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>20141978</t>
-  </si>
-  <si>
-    <t>GARNIER VITC LWPH100</t>
-  </si>
-  <si>
-    <t>20141979</t>
-  </si>
-  <si>
-    <t>GARNIER SKR GLOW 100</t>
-  </si>
-  <si>
-    <t>20142123</t>
-  </si>
-  <si>
-    <t>BDL FW PAPAYA 100G</t>
-  </si>
-  <si>
-    <t>20110001</t>
-  </si>
-  <si>
-    <t>WARDAH UV GRD GEL40</t>
-  </si>
-  <si>
-    <t>20127466</t>
-  </si>
-  <si>
-    <t>IMPLRA SPF40 SS 50ML</t>
-  </si>
-  <si>
-    <t>10028739</t>
-  </si>
-  <si>
-    <t>VIVA MILK CLN BGK100</t>
-  </si>
-  <si>
-    <t>RT,(E-7B)</t>
-  </si>
-  <si>
-    <t>20135594</t>
-  </si>
-  <si>
-    <t>CARASUN SS UV.SUNS30</t>
-  </si>
-  <si>
-    <t>20138590</t>
-  </si>
-  <si>
-    <t>HNSUI BRGH/E MOIS 30</t>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMNYES HKTA CHKN 88G</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20133672</t>
-  </si>
-  <si>
-    <t>HNSUI COL.SUNS.SPF50</t>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMNYES TKYO CHKN 84G</t>
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20138592</t>
-  </si>
-  <si>
-    <t>HNSUI MICELAR WTR300</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
 </sst>
 </file>
@@ -637,14 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -865,15 +870,15 @@
         <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -882,10 +887,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -905,15 +910,15 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -930,10 +935,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -945,15 +950,15 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -965,55 +970,55 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1022,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>9</v>
@@ -1030,10 +1035,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1042,7 +1047,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -1050,10 +1055,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1062,7 +1067,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -1070,50 +1075,50 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1122,18 +1127,18 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1142,18 +1147,18 @@
         <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1162,18 +1167,18 @@
         <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1182,10 +1187,10 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1202,10 +1207,10 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,10 +1227,10 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,18 +1247,18 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1262,10 +1267,30 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>33</v>
+      <c r="B32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -238,7 +238,7 @@
     <t>20141464</t>
   </si>
   <si>
-    <t>RMNYES HKTA CHKN 88G</t>
+    <t>RMN YES HKTA CHKN88G</t>
   </si>
   <si>
     <t>8</t>
@@ -247,7 +247,7 @@
     <t>20141466</t>
   </si>
   <si>
-    <t>RMNYES TKYO CHKN 84G</t>
+    <t>RMN YES TKYO CHKN84G</t>
   </si>
   <si>
     <t>9</t>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -97,7 +97,7 @@
     <t>20102790</t>
   </si>
   <si>
-    <t>ABC MILK COFFEE 200</t>
+    <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
     <t>6</t>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004061</t>
-  </si>
-  <si>
-    <t>W/COCO ICE BON2 5'S</t>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
   </si>
   <si>
     <t>EG0A</t>
@@ -28,15 +28,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -52,46 +43,28 @@
     <t>4</t>
   </si>
   <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>20102790</t>
@@ -643,14 +616,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -687,18 +660,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -707,10 +680,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -724,13 +697,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,213 +717,213 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -964,193 +937,193 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,13 +1137,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,113 +1157,33 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
   <si>
     <t/>
   </si>
@@ -616,17 +616,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,8 +646,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -662,11 +669,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -682,11 +689,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -702,11 +709,11 @@
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -722,11 +729,11 @@
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -742,11 +749,11 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -762,11 +769,11 @@
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -782,11 +789,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -802,11 +809,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -822,11 +829,11 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -842,11 +849,11 @@
       <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -862,11 +869,11 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -882,11 +889,11 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -902,11 +909,11 @@
       <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -922,11 +929,11 @@
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -942,11 +949,11 @@
       <c r="E16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -962,11 +969,11 @@
       <c r="E17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
@@ -982,11 +989,11 @@
       <c r="E18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1002,11 +1009,11 @@
       <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -1022,11 +1029,11 @@
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
@@ -1042,11 +1049,11 @@
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1062,11 +1069,11 @@
       <c r="E22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -1082,11 +1089,11 @@
       <c r="E23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -1102,11 +1109,11 @@
       <c r="E24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>60</v>
       </c>
@@ -1122,11 +1129,11 @@
       <c r="E25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1142,11 +1149,11 @@
       <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -1162,11 +1169,11 @@
       <c r="E27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
@@ -1182,7 +1189,7 @@
       <c r="E28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
   <si>
     <t/>
   </si>
@@ -616,18 +616,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -646,14 +645,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -669,11 +662,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -689,11 +682,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -709,11 +702,11 @@
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -729,11 +722,11 @@
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -749,11 +742,11 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -769,11 +762,11 @@
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -789,11 +782,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -809,11 +802,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -829,11 +822,11 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -849,11 +842,11 @@
       <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -869,11 +862,11 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -889,11 +882,11 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -909,11 +902,11 @@
       <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -929,11 +922,11 @@
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -949,11 +942,11 @@
       <c r="E16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -969,11 +962,11 @@
       <c r="E17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
@@ -989,11 +982,11 @@
       <c r="E18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1009,11 +1002,11 @@
       <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -1029,11 +1022,11 @@
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
@@ -1049,11 +1042,11 @@
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1069,11 +1062,11 @@
       <c r="E22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -1089,11 +1082,11 @@
       <c r="E23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -1109,11 +1102,11 @@
       <c r="E24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>60</v>
       </c>
@@ -1129,11 +1122,11 @@
       <c r="E25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1149,11 +1142,11 @@
       <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -1169,11 +1162,11 @@
       <c r="E27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
@@ -1189,7 +1182,7 @@
       <c r="E28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -124,7 +124,7 @@
     <t>20055311</t>
   </si>
   <si>
-    <t>NABATI RCHSE WFR 110</t>
+    <t>NABATI RCHSE WFR 100</t>
   </si>
   <si>
     <t>20022908</t>
